--- a/0.EJEMPLOS_EXAMPLES/NUM ROMANOS/NUM ROMANOS - FORMULA FILE.xlsx
+++ b/0.EJEMPLOS_EXAMPLES/NUM ROMANOS/NUM ROMANOS - FORMULA FILE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\FTP\z. V8.0\0.EJEMPLOS_EXAMPLES\NUM ROMANOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\0.EJEMPLOS_EXAMPLES\NUM ROMANOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB09D6D-0A9F-4A87-B410-3C013B03B960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A8BF36-FC07-481A-9899-CC57712D6BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12266" tabRatio="805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" tabRatio="805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas DG" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="280">
   <si>
     <t>DATO_01</t>
   </si>
@@ -670,9 +670,6 @@
     <t>=SI(Dato_20=Dato_18;"VERDADERO";"FALSO")</t>
   </si>
   <si>
-    <t>V - 8.0</t>
-  </si>
-  <si>
     <t>=ALEATORIO.ENTRE(10;100)</t>
   </si>
   <si>
@@ -689,42 +686,6 @@
   </si>
   <si>
     <t>=NUMERO.ROMANO(MAX(Dato_01-ALEATORIO.ENTRE(6;10);1))</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P01_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P02_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P03_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P04_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P05_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P06_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P07_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P08_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P09_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P10_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P11_1)</t>
-  </si>
-  <si>
-    <t>=NUMERO.ROMANO(P12_1)</t>
   </si>
   <si>
     <t>=ALEATORIO.ENTRE(5;100)</t>
@@ -811,7 +772,121 @@
 3. Escribe el número de "&amp;Dato_19&amp;"{1:NUMERICAL:%100%"&amp;Dato_03&amp;":0#Muy bien~%-50%"&amp;Dato_02&amp;":0#Debes estudiar mas}"</t>
   </si>
   <si>
-    <t>="El Numero Romano de "&amp;@Dato_01&amp;" es:"</t>
+    <t>=NUMERO.ROMANO(P_01_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_02_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_03_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_04_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_05_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_06_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_07_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_08_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_09_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_10_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_11_1)</t>
+  </si>
+  <si>
+    <t>=NUMERO.ROMANO(P_12_1)</t>
+  </si>
+  <si>
+    <t>P_01_1</t>
+  </si>
+  <si>
+    <t>P_01_2</t>
+  </si>
+  <si>
+    <t>P_02_1</t>
+  </si>
+  <si>
+    <t>P_02_2</t>
+  </si>
+  <si>
+    <t>P_03_1</t>
+  </si>
+  <si>
+    <t>P_03_2</t>
+  </si>
+  <si>
+    <t>P_04_1</t>
+  </si>
+  <si>
+    <t>P_04_2</t>
+  </si>
+  <si>
+    <t>P_05_1</t>
+  </si>
+  <si>
+    <t>P_05_2</t>
+  </si>
+  <si>
+    <t>P_06_1</t>
+  </si>
+  <si>
+    <t>P_06_2</t>
+  </si>
+  <si>
+    <t>P_07_1</t>
+  </si>
+  <si>
+    <t>P_07_2</t>
+  </si>
+  <si>
+    <t>P_08_1</t>
+  </si>
+  <si>
+    <t>P_08_2</t>
+  </si>
+  <si>
+    <t>P_09_1</t>
+  </si>
+  <si>
+    <t>P_09_2</t>
+  </si>
+  <si>
+    <t>P_10_1</t>
+  </si>
+  <si>
+    <t>P_10_2</t>
+  </si>
+  <si>
+    <t>P_11_1</t>
+  </si>
+  <si>
+    <t>P_11_2</t>
+  </si>
+  <si>
+    <t>P_12_1</t>
+  </si>
+  <si>
+    <t>P_12_2</t>
+  </si>
+  <si>
+    <t>V - 8.3</t>
+  </si>
+  <si>
+    <t>ad2</t>
+  </si>
+  <si>
+    <t>="El Numero Romano de "&amp;Dato_01&amp;" es:"</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1927,7 @@
     </row>
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -1987,7 +2062,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zF1LcP4fsViw04E1VFmHE1+1KrGPDH3Tt4iwGPOG0/JfouJwLfgc388ilXycAOD+KcijZul0lWX1/gt3JmG10w==" saltValue="3W2i2PG98gO/3sdL7kdI0Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5ozhgns7FIGVBCLq4ng7yphS+UAvjFOziR5PFpncILZemYXHTd6Ekr4rQ6lI8xOlq6wVcL+z55+TO4hB6boktw==" saltValue="7hP4sB5n0iGwJHNBIPr7Fw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -2466,7 +2541,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas DG'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -2505,7 +2580,7 @@
         <v>33</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="AG40" s="10"/>
       <c r="AJ40" s="10"/>
@@ -2792,7 +2867,7 @@
     </row>
     <row r="64" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lULXXzw0+l/9oEiwRlIHHeIDxMCANGYOupI0qI5g3JXglpWPZqskwNd7eDRA1TRibbIAlBb0kt80UV6litK/FA==" saltValue="8DrJKEqISUUn4JgiuGyhzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ym7/FGHPU07+k7CR5A2c/7z43zdzx38PSHOWbnd38mNcnE4qrnhAyh2fWUdyzs6hP0EWtyziFygVZ1Li3b87dw==" saltValue="sN/CUjLwYyjYOhyMi+sjLA==" spinCount="100000" sheet="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -2883,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -3268,7 +3343,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -3307,7 +3382,7 @@
         <v>33</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG40" s="10"/>
       <c r="AJ40" s="10"/>
@@ -3320,7 +3395,7 @@
         <v>40</v>
       </c>
       <c r="AD41" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG41" s="10"/>
       <c r="AJ41" s="10"/>
@@ -3333,7 +3408,7 @@
         <v>41</v>
       </c>
       <c r="AD42" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG42" s="10"/>
       <c r="AJ42" s="10"/>
@@ -3346,7 +3421,7 @@
         <v>42</v>
       </c>
       <c r="AD43" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG43" s="10"/>
       <c r="AJ43" s="10"/>
@@ -3359,7 +3434,7 @@
         <v>43</v>
       </c>
       <c r="AD44" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG44" s="10"/>
       <c r="AJ44" s="10"/>
@@ -4077,7 +4152,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -4706,7 +4781,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -4755,7 +4830,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>62</v>
+        <v>253</v>
       </c>
       <c r="AD41" s="24" t="s">
         <v>186</v>
@@ -4768,10 +4843,10 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="AD42" s="24" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="AG42" s="10"/>
       <c r="AJ42" s="10"/>
@@ -4781,7 +4856,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="AD43" s="24" t="s">
         <v>187</v>
@@ -4794,10 +4869,10 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="AD44" s="24" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="AG44" s="10"/>
       <c r="AJ44" s="10"/>
@@ -4807,7 +4882,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="AD45" s="24" t="s">
         <v>188</v>
@@ -4820,10 +4895,10 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="AD46" s="24" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="AG46" s="10"/>
       <c r="AJ46" s="10"/>
@@ -4833,7 +4908,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="AD47" s="24" t="s">
         <v>189</v>
@@ -4846,10 +4921,10 @@
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC48" s="9" t="s">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="AD48" s="24" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="AG48" s="10"/>
       <c r="AJ48" s="10"/>
@@ -4859,7 +4934,7 @@
     </row>
     <row r="49" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC49" s="9" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="AD49" s="24" t="s">
         <v>190</v>
@@ -4872,10 +4947,10 @@
     </row>
     <row r="50" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC50" s="9" t="s">
-        <v>71</v>
+        <v>262</v>
       </c>
       <c r="AD50" s="24" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="AG50" s="10"/>
       <c r="AJ50" s="10"/>
@@ -4885,7 +4960,7 @@
     </row>
     <row r="51" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC51" s="9" t="s">
-        <v>72</v>
+        <v>263</v>
       </c>
       <c r="AD51" s="24" t="s">
         <v>191</v>
@@ -4898,10 +4973,10 @@
     </row>
     <row r="52" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC52" s="9" t="s">
-        <v>73</v>
+        <v>264</v>
       </c>
       <c r="AD52" s="24" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="AG52" s="10"/>
       <c r="AJ52" s="10"/>
@@ -4911,7 +4986,7 @@
     </row>
     <row r="53" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC53" s="9" t="s">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AD53" s="24" t="s">
         <v>192</v>
@@ -4924,10 +4999,10 @@
     </row>
     <row r="54" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC54" s="9" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="AD54" s="24" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="AG54" s="10"/>
       <c r="AJ54" s="10"/>
@@ -4937,7 +5012,7 @@
     </row>
     <row r="55" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC55" s="9" t="s">
-        <v>76</v>
+        <v>267</v>
       </c>
       <c r="AD55" s="24" t="s">
         <v>193</v>
@@ -4950,10 +5025,10 @@
     </row>
     <row r="56" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC56" s="9" t="s">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AD56" s="24" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="AG56" s="10"/>
       <c r="AJ56" s="10"/>
@@ -4963,7 +5038,7 @@
     </row>
     <row r="57" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC57" s="9" t="s">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="AD57" s="24" t="s">
         <v>194</v>
@@ -4976,10 +5051,10 @@
     </row>
     <row r="58" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC58" s="9" t="s">
-        <v>78</v>
+        <v>270</v>
       </c>
       <c r="AD58" s="24" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="AG58" s="10"/>
       <c r="AJ58" s="10"/>
@@ -4989,7 +5064,7 @@
     </row>
     <row r="59" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC59" s="9" t="s">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="AD59" s="24" t="s">
         <v>195</v>
@@ -5002,10 +5077,10 @@
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC60" s="9" t="s">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="AD60" s="24" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="AG60" s="10"/>
       <c r="AJ60" s="10"/>
@@ -5015,7 +5090,7 @@
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AD61" s="24" t="s">
         <v>196</v>
@@ -5028,10 +5103,10 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AD62" s="24" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="AG62" s="10"/>
       <c r="AJ62" s="10"/>
@@ -5041,7 +5116,7 @@
     </row>
     <row r="63" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC63" s="9" t="s">
-        <v>83</v>
+        <v>275</v>
       </c>
       <c r="AD63" s="24" t="s">
         <v>197</v>
@@ -5054,10 +5129,10 @@
     </row>
     <row r="64" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC64" s="13" t="s">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AD64" s="25" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="AG64" s="20"/>
       <c r="AJ64" s="20"/>
@@ -5122,7 +5197,7 @@
     </row>
     <row r="70" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1GqnPTxL2T0Dm6MaXvz9Y23MakD4UmSeRKKy6tt6GG5kPNgzFFp4j/C4xVOAJ46Y5aIC5GtEBP8JYHALtHsgVg==" saltValue="cDfc5yt23g9UF8iJUezx3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YakR6Z7xcs5d59Je3QOnCq2ak8tUmNrOQTupW75U5hWAcfnextc4Hr0if0QjK5HNq69M74G8z81rvhqJhTLoOQ==" saltValue="wRGlybiDiRy52iM/6xRYLg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -5215,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="26" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -5600,7 +5675,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -5652,7 +5727,7 @@
         <v>33</v>
       </c>
       <c r="AD41" s="24" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="AG41" s="10"/>
       <c r="AJ41" s="10"/>
@@ -5704,7 +5779,7 @@
         <v>41</v>
       </c>
       <c r="AD45" s="24" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="AG45" s="10"/>
       <c r="AJ45" s="10"/>
@@ -6036,7 +6111,7 @@
     <row r="1" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC1"/>
       <c r="AD1" s="14" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="AG1" s="14"/>
       <c r="AJ1" s="14"/>
@@ -6161,7 +6236,7 @@
         <v>5</v>
       </c>
       <c r="AD10" s="24" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="AG10" s="10"/>
       <c r="AJ10" s="10"/>
@@ -6175,7 +6250,7 @@
         <v>6</v>
       </c>
       <c r="AD11" s="24" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="AG11" s="10"/>
       <c r="AJ11" s="10"/>
@@ -6189,7 +6264,7 @@
         <v>7</v>
       </c>
       <c r="AD12" s="24" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="AG12" s="10"/>
       <c r="AJ12" s="10"/>
@@ -6301,7 +6376,7 @@
         <v>16</v>
       </c>
       <c r="AD21" s="24" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="AG21" s="10"/>
       <c r="AJ21" s="10"/>
@@ -6351,7 +6426,7 @@
         <v>20</v>
       </c>
       <c r="AD25" s="24" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="AG25" s="10"/>
       <c r="AJ25" s="10"/>
@@ -6494,7 +6569,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -6533,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="AG40" s="10"/>
       <c r="AJ40" s="10"/>
@@ -6559,7 +6634,7 @@
         <v>63</v>
       </c>
       <c r="AD42" s="24" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="AG42" s="10"/>
       <c r="AJ42" s="10"/>
@@ -6585,7 +6660,7 @@
         <v>65</v>
       </c>
       <c r="AD44" s="24" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="AG44" s="10"/>
       <c r="AJ44" s="10"/>
@@ -6611,7 +6686,7 @@
         <v>67</v>
       </c>
       <c r="AD46" s="24" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AG46" s="10"/>
       <c r="AJ46" s="10"/>
@@ -6637,7 +6712,7 @@
         <v>69</v>
       </c>
       <c r="AD48" s="24" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AG48" s="10"/>
       <c r="AJ48" s="10"/>
@@ -6663,7 +6738,7 @@
         <v>71</v>
       </c>
       <c r="AD50" s="24" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="AG50" s="10"/>
       <c r="AJ50" s="10"/>
@@ -6689,7 +6764,7 @@
         <v>73</v>
       </c>
       <c r="AD52" s="24" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AG52" s="10"/>
       <c r="AJ52" s="10"/>
@@ -6715,7 +6790,7 @@
         <v>75</v>
       </c>
       <c r="AD54" s="24" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="AG54" s="10"/>
       <c r="AJ54" s="10"/>
@@ -6741,7 +6816,7 @@
         <v>77</v>
       </c>
       <c r="AD56" s="24" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="AG56" s="10"/>
       <c r="AJ56" s="10"/>
@@ -6935,8 +7010,8 @@
   <sheetData>
     <row r="1" spans="1:45" hidden="1" x14ac:dyDescent="0.5">
       <c r="AC1"/>
-      <c r="AD1">
-        <v>9</v>
+      <c r="AD1" t="s">
+        <v>185</v>
       </c>
       <c r="AG1"/>
       <c r="AJ1"/>
@@ -6946,7 +7021,9 @@
     </row>
     <row r="2" spans="1:45" hidden="1" x14ac:dyDescent="0.5">
       <c r="AC2"/>
-      <c r="AD2"/>
+      <c r="AD2">
+        <v>1</v>
+      </c>
       <c r="AG2"/>
       <c r="AJ2"/>
       <c r="AM2"/>
@@ -6955,7 +7032,9 @@
     </row>
     <row r="3" spans="1:45" ht="14.7" hidden="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC3"/>
-      <c r="AD3"/>
+      <c r="AD3">
+        <v>9</v>
+      </c>
       <c r="AG3"/>
       <c r="AJ3"/>
       <c r="AM3"/>
@@ -6987,7 +7066,7 @@
         <v>0</v>
       </c>
       <c r="AD5" s="26" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -7372,7 +7451,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -7411,7 +7490,7 @@
         <v>33</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="AG40" s="10"/>
       <c r="AJ40" s="10"/>
@@ -7535,7 +7614,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="44GY6EUN6CnFhh0k94oIlIEjDUJ8S5qqo2XL+MPwmnBLGnk0WIYhiwnWWTcOzJn74K6Fyhr5KLyllfQ/VRz23g==" saltValue="kGmGTIvnRn4mtnWiA2LvQQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rS/cRcEuPNMBm3uWIFLQjptrQJuz7JhmpBNJpkMU7CnIScysRgLiu5P67GD42S/zBCut9UUiZ7TqKw0semKSww==" saltValue="QeUDD2WjdmveEEze8c/iHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -7569,8 +7648,8 @@
   <sheetData>
     <row r="1" spans="1:45" ht="14.7" hidden="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC1"/>
-      <c r="AD1">
-        <v>3</v>
+      <c r="AD1" t="s">
+        <v>185</v>
       </c>
       <c r="AG1"/>
       <c r="AJ1"/>
@@ -7580,7 +7659,9 @@
     </row>
     <row r="2" spans="1:45" ht="14.7" hidden="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC2"/>
-      <c r="AD2"/>
+      <c r="AD2">
+        <v>8</v>
+      </c>
       <c r="AG2"/>
       <c r="AJ2"/>
       <c r="AM2"/>
@@ -7589,7 +7670,9 @@
     </row>
     <row r="3" spans="1:45" ht="14.7" hidden="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC3"/>
-      <c r="AD3"/>
+      <c r="AD3">
+        <v>3</v>
+      </c>
       <c r="AG3"/>
       <c r="AJ3"/>
       <c r="AM3"/>
@@ -7635,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="AD6" s="24" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="AG6" s="10"/>
       <c r="AJ6" s="10"/>
@@ -7649,7 +7732,7 @@
         <v>2</v>
       </c>
       <c r="AD7" s="24" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="AG7" s="10"/>
       <c r="AJ7" s="10"/>
@@ -7663,7 +7746,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="24" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="AG8" s="10"/>
       <c r="AJ8" s="10"/>
@@ -7823,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="AD21" s="24" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="AG21" s="10"/>
       <c r="AJ21" s="10"/>
@@ -7837,7 +7920,7 @@
         <v>17</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="AG22" s="10"/>
       <c r="AJ22" s="10"/>
@@ -7851,7 +7934,7 @@
         <v>18</v>
       </c>
       <c r="AD23" s="24" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="AG23" s="10"/>
       <c r="AJ23" s="10"/>
@@ -7865,7 +7948,7 @@
         <v>19</v>
       </c>
       <c r="AD24" s="24" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="AG24" s="10"/>
       <c r="AJ24" s="10"/>
@@ -8020,7 +8103,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -8059,7 +8142,7 @@
         <v>33</v>
       </c>
       <c r="AD40" s="24" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="AG40" s="10"/>
       <c r="AJ40" s="10"/>
@@ -8137,7 +8220,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9aQQpAsDYyDahEWTLct5CLvlXjZ+/kLuGa+GNirJaeb3hSuqxMdkpdH5QPADfVeipswfgpeTvPA1jyQ1gtQ6bg==" saltValue="Wg5WFvfHQf/eWm1+28204Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9/zybYCIsQJqCrCKv0c82W7EXpYepM+Yq82n606mNsRi5bAuBIPC2Q0Tx6PyM2td+htBB95noj+aHk30UQJOjg==" saltValue="Seg1lQQp0OttR1fYoDsCOw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
